--- a/Daily/Daily G4 - Corte 12 mayo.xlsx
+++ b/Daily/Daily G4 - Corte 12 mayo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unisabanaedu-my.sharepoint.com/personal/yosimardiamo_unisabana_edu_co/Documents/Documentos/0.7 Clases Unisabana 2026-1/2. Capstone Design Project/Dailyes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="8_{51AB3442-67E6-45BF-B1E3-1F61098ECF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B897E2C-07B7-4666-BA45-A60CD2DAF0A9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87D6907-EC59-4A0F-B5BC-074281BFF497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F726620C-8D1F-4C8C-B0B8-6A75EE127E99}"/>
   </bookViews>
@@ -38,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="72">
   <si>
     <t>Fase</t>
   </si>
@@ -98,15 +120,9 @@
     <t>Diagrama completo de navegación del usuario.</t>
   </si>
   <si>
-    <t>Pendiente en el trabajo</t>
-  </si>
-  <si>
     <t>Sergio</t>
   </si>
   <si>
-    <t>28 de abril</t>
-  </si>
-  <si>
     <t>Wireframes / Prototipo</t>
   </si>
   <si>
@@ -233,18 +249,9 @@
     <t>Pendente Documento</t>
   </si>
   <si>
-    <t>13 de mayo</t>
-  </si>
-  <si>
     <t>Todos</t>
   </si>
   <si>
-    <t>13 de mayo - Pendiente conectarlo al Back</t>
-  </si>
-  <si>
-    <t>Ricardo</t>
-  </si>
-  <si>
     <t>20 de mayo - Excel</t>
   </si>
   <si>
@@ -267,6 +274,9 @@
   </si>
   <si>
     <t>Ventas - Costos - Gastos - Depreciación - EBIT - NOPAT - Depreciación - FEO (Flujo de efectivo de operación) - CAPEX (Ley 1819 de 1016) Vida útil de los activos, capital de trabajo</t>
+  </si>
+  <si>
+    <t>Christian y Daniel</t>
   </si>
 </sst>
 </file>
@@ -757,7 +767,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
@@ -768,289 +778,272 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6"/>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5"/>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>21</v>
+      <c r="G9" s="3" t="e" cm="1">
+        <f t="array" ref="G9">G928 de abril</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="6"/>
       <c r="C11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="G11" s="3"/>
     </row>
     <row r="12" spans="2:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="6"/>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
       <c r="C13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="E14" s="2" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
       <c r="C15" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5"/>
       <c r="C16" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>66</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="G16" s="3"/>
     </row>
     <row r="17" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="E17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5"/>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="6"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="6"/>
       <c r="C22" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1058,107 +1051,107 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="6"/>
       <c r="C25" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="5"/>
       <c r="C26" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="E27" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="5"/>
       <c r="C28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
